--- a/public/templates/user-import-template.xlsx
+++ b/public/templates/user-import-template.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="用户批量导入模板" sheetId="1" r:id="rId1"/>
+    <sheet name="格式说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>学号</t>
   </si>
@@ -47,16 +48,13 @@
     <t>年级</t>
   </si>
   <si>
-    <t>示例数据，导入时需删除</t>
-  </si>
-  <si>
-    <t>123456</t>
+    <t>@Student20254227001</t>
   </si>
   <si>
     <t>张三</t>
   </si>
   <si>
-    <t>zhangsan@stu.suda.edu.cn</t>
+    <t>init@qq.com</t>
   </si>
   <si>
     <t>计算机科学与技术</t>
@@ -65,6 +63,9 @@
     <t>2024-硕</t>
   </si>
   <si>
+    <t>@Student20254227002</t>
+  </si>
+  <si>
     <t>李四</t>
   </si>
   <si>
@@ -75,6 +76,24 @@
   </si>
   <si>
     <t>2024-博</t>
+  </si>
+  <si>
+    <t>严格限制为11为数字</t>
+  </si>
+  <si>
+    <t>要求至少分别包括1个大写，小写字母，数字，特殊字符及密码长度不小于10位</t>
+  </si>
+  <si>
+    <t>只允许包含简体中文</t>
+  </si>
+  <si>
+    <t>满足邮箱基本格式要求，初始邮箱可设置为init@qq.com，用户首次登录时系统可以引导邮箱修改初始邮箱和密码</t>
+  </si>
+  <si>
+    <t>无格式检查</t>
+  </si>
+  <si>
+    <t>2024-硕，2024-博，限制为四位数字-硕/博</t>
   </si>
 </sst>
 </file>
@@ -111,6 +130,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
@@ -130,13 +156,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -581,16 +600,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -711,18 +730,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1071,11 +1093,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="26.3636363636364" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="1" max="1" width="26.3611111111111" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
@@ -1083,81 +1105,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3">
+        <v>20254227001</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2">
-        <v>20254227001</v>
+      <c r="A3" s="3">
+        <v>20254227002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2">
-        <v>20254227002</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" display="zhangsan@stu.suda.edu.cn"/>
-    <hyperlink ref="D4" r:id="rId2" display="lisi@stu.suda.edu.cn"/>
+    <hyperlink ref="D2" r:id="rId1" display="init@qq.com" tooltip="mailto:init@qq.com"/>
+    <hyperlink ref="D3" r:id="rId2" display="lisi@stu.suda.edu.cn"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="15.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="107.111111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="50" customHeight="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="50" customHeight="1" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>